--- a/data/trans_camb/IP25-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Estudios-trans_camb.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -63,13 +63,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -504,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +508,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,21 +523,18 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -564,37 +551,22 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2012/2007</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
+          <t>2016/2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>2012/2007</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
         </is>
       </c>
     </row>
@@ -607,9 +579,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -634,37 +603,22 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-92,94</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>5,88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,88</t>
+          <t>3,03</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-89,22</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
           <t>1,28</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-91,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 7,06</t>
+          <t>-5,47; 7,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 3,18</t>
+          <t>-11,6; 2,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-96,39; -87,12</t>
+          <t>-1,39; 12,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 11,98</t>
+          <t>-0,59; 12,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 12,22</t>
+          <t>-1,4; 7,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,48; -82,67</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-1,26; 7,81</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-3,79; 6,17</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>-94,0; -87,16</t>
+          <t>-3,94; 6,25</t>
         </is>
       </c>
     </row>
@@ -740,37 +679,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
           <t>1,4%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -783,47 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 7,99</t>
+          <t>-5,74; 8,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 3,41</t>
+          <t>-12,2; 3,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,53; 14,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 14,33</t>
+          <t>-0,61; 15,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 14,43</t>
+          <t>-1,48; 8,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-1,36; 8,88</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-4,11; 6,93</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-4,24; 6,98</t>
         </is>
       </c>
     </row>
@@ -850,37 +759,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-91,05</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,8</t>
+          <t>0,17</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-88,76</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
           <t>2,07</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>-89,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 0,38</t>
+          <t>-6,08; 0,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,27</t>
+          <t>-2,86; 3,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-93,04; -88,64</t>
+          <t>-0,27; 6,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 6,51</t>
+          <t>0,76; 7,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,75</t>
+          <t>-2,1; 2,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-91,12; -86,47</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 2,45</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-0,03; 4,03</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>-91,38; -88,16</t>
+          <t>0,03; 4,22</t>
         </is>
       </c>
     </row>
@@ -956,37 +835,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>2,31%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 0,4</t>
+          <t>-6,63; 0,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 3,68</t>
+          <t>-3,08; 3,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,27; 7,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 7,53</t>
+          <t>0,88; 8,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,75</t>
+          <t>-2,32; 2,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-2,66; 2,76</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-0,03; 4,58</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>0,03; 4,78</t>
         </is>
       </c>
     </row>
@@ -1066,37 +915,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-87,16</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,09</t>
+          <t>3,84</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,84</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-82,88</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,54</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
           <t>1,38</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>-85,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 8,39</t>
+          <t>-3,48; 7,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 4,86</t>
+          <t>-6,76; 5,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-90,99; -82,66</t>
+          <t>-1,24; 11,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 11,72</t>
+          <t>-2,2; 9,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 10,25</t>
+          <t>-0,4; 8,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-86,91; -77,25</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-0,79; 7,91</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-2,75; 5,85</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>-87,97; -81,58</t>
+          <t>-2,48; 5,7</t>
         </is>
       </c>
     </row>
@@ -1172,37 +991,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
           <t>1,62%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 9,88</t>
+          <t>-3,81; 9,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 5,74</t>
+          <t>-7,44; 6,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,25; 14,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 14,8</t>
+          <t>-2,47; 12,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 12,99</t>
+          <t>-0,42; 9,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 9,57</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>-3,15; 7,03</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-2,87; 6,94</t>
         </is>
       </c>
     </row>
@@ -1282,37 +1071,22 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-90,31</t>
+          <t>3,72</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,8</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-87,52</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
           <t>1,72</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>-88,88</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 1,47</t>
+          <t>-3,92; 1,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 2,18</t>
+          <t>-3,33; 1,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-91,99; -88,39</t>
+          <t>1,31; 6,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,29</t>
+          <t>1,14; 6,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 6,58</t>
+          <t>-0,44; 3,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-89,46; -85,52</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-0,57; 3,23</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-0,18; 3,42</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>-90,18; -87,49</t>
+          <t>-0,03; 3,78</t>
         </is>
       </c>
     </row>
@@ -1388,37 +1147,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
           <t>1,94%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,66</t>
+          <t>-4,27; 1,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 2,46</t>
+          <t>-3,66; 2,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,49; 7,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,3</t>
+          <t>1,31; 7,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,67</t>
+          <t>-0,49; 3,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-0,64; 3,67</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>-0,2; 3,88</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-0,03; 4,32</t>
         </is>
       </c>
     </row>
@@ -1485,11 +1214,11 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A16:A19"/>
   </mergeCells>

--- a/data/trans_camb/IP25-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 7,2</t>
+          <t>-5,11; 6,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 2,89</t>
+          <t>-11,64; 3,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 12,2</t>
+          <t>-1,43; 11,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 12,65</t>
+          <t>-0,66; 13,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 7,26</t>
+          <t>-1,34; 7,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 6,25</t>
+          <t>-4,3; 6,17</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 8,04</t>
+          <t>-5,36; 7,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 3,23</t>
+          <t>-12,41; 3,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 14,4</t>
+          <t>-1,54; 13,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 15,12</t>
+          <t>-0,64; 16,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 8,3</t>
+          <t>-1,45; 9,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 6,98</t>
+          <t>-4,6; 6,96</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 0,24</t>
+          <t>-6,29; 0,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,2</t>
+          <t>-2,68; 3,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 6,2</t>
+          <t>-0,05; 6,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,14</t>
+          <t>0,95; 6,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,5</t>
+          <t>-2,03; 2,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,22</t>
+          <t>-0,04; 4,14</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 0,27</t>
+          <t>-6,85; 0,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 3,59</t>
+          <t>-2,91; 3,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 7,14</t>
+          <t>-0,05; 7,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,24</t>
+          <t>1,05; 7,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,82</t>
+          <t>-2,23; 2,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,78</t>
+          <t>-0,03; 4,67</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 7,51</t>
+          <t>-3,33; 7,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,08</t>
+          <t>-7,26; 4,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 11,2</t>
+          <t>-0,71; 11,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 9,94</t>
+          <t>-2,67; 9,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 8,06</t>
+          <t>-0,96; 7,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,7</t>
+          <t>-2,81; 5,71</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 9,0</t>
+          <t>-3,75; 9,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 6,08</t>
+          <t>-8,02; 5,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 14,13</t>
+          <t>-0,94; 14,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 12,64</t>
+          <t>-2,92; 12,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 9,93</t>
+          <t>-1,08; 9,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 6,94</t>
+          <t>-3,2; 6,92</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,42</t>
+          <t>-3,74; 1,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,96</t>
+          <t>-3,02; 2,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,45</t>
+          <t>1,31; 6,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,44</t>
+          <t>1,15; 6,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,35</t>
+          <t>-0,49; 3,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,78</t>
+          <t>-0,03; 3,64</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,6</t>
+          <t>-4,13; 1,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,2</t>
+          <t>-3,28; 2,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 7,53</t>
+          <t>1,51; 7,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,51</t>
+          <t>1,32; 7,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,8</t>
+          <t>-0,53; 3,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,32</t>
+          <t>-0,04; 4,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP25-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Estudios-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,91</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-3,67</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 6,43</t>
+          <t>-1,3; 11,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 3,32</t>
+          <t>-1,84; 12,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 11,44</t>
+          <t>-4,62; 7,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 13,17</t>
+          <t>-12,16; 3,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 7,92</t>
+          <t>-1,26; 7,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 6,17</t>
+          <t>-3,79; 6,17</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-3,94%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 7,21</t>
+          <t>-1,32; 14,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 3,63</t>
+          <t>-1,9; 14,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 13,64</t>
+          <t>-4,76; 7,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 16,05</t>
+          <t>-12,65; 3,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 9,02</t>
+          <t>-1,36; 8,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 6,96</t>
+          <t>-4,11; 6,93</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3,07</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-3,05</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 0,44</t>
+          <t>-0,31; 6,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,03</t>
+          <t>0,68; 6,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 6,39</t>
+          <t>-6,27; 0,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 6,82</t>
+          <t>-2,75; 3,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,36</t>
+          <t>-2,42; 2,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,14</t>
+          <t>-0,03; 4,03</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-3,34%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 0,49</t>
+          <t>-0,34; 7,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,35</t>
+          <t>0,75; 7,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 7,37</t>
+          <t>-6,79; 0,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,8</t>
+          <t>-2,93; 3,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,66</t>
+          <t>-2,66; 2,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,67</t>
+          <t>-0,03; 4,58</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,09</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,84</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,92</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 7,62</t>
+          <t>-1,09; 11,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 4,9</t>
+          <t>-2,4; 10,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 11,34</t>
+          <t>-3,34; 8,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 9,84</t>
+          <t>-7,23; 4,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 7,74</t>
+          <t>-0,79; 7,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 5,71</t>
+          <t>-2,75; 5,85</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>2,52%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-1,05%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 9,0</t>
+          <t>-1,28; 14,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 5,89</t>
+          <t>-2,8; 12,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 14,22</t>
+          <t>-3,73; 9,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 12,56</t>
+          <t>-8,01; 5,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 9,33</t>
+          <t>-0,9; 9,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 6,92</t>
+          <t>-3,15; 7,03</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,72</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-1,23</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-0,48</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,8</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,66</t>
+          <t>0,95; 6,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,2</t>
+          <t>1,33; 6,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,42</t>
+          <t>-3,85; 1,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,33</t>
+          <t>-2,99; 2,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,35</t>
+          <t>-0,57; 3,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,64</t>
+          <t>-0,18; 3,42</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-1,36%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-0,54%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,85</t>
+          <t>1,05; 7,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 2,47</t>
+          <t>1,48; 7,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,51; 7,46</t>
+          <t>-4,22; 1,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,39</t>
+          <t>-3,26; 2,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,84</t>
+          <t>-0,64; 3,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 4,17</t>
+          <t>-0,2; 3,88</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP25-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP25-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,319 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,88</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,67</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>5.260214161461086</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5.8843902662161</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.911229481425524</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-3.665384803355931</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>3.032726128245511</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1.277850400629332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,3; 11,98</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-1,84; 12,22</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,62; 7,06</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-12,16; 3,18</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-1,26; 7,81</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-3,79; 6,17</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.296774021442126</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.83816917725407</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.621707138377131</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-12.16475853874858</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-1.259250652317825</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-3.789142352988963</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,9%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,6%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-3,94%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.98356932481865</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>12.22118000843774</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>7.064417941205142</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.177859159785994</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>7.81485530790122</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>6.167957924598891</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,32; 14,33</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,9; 14,43</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-4,76; 7,99</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-12,65; 3,41</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-1,36; 8,88</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-4,11; 6,93</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.05895883421574277</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.06595487931050316</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.009804921089346007</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.03943991002438858</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.03328304469099929</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.01402393430664385</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,8</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,05</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,07</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-0.01318393945203295</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.01903768913475655</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.04760114329140202</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.1264875528550287</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.01361746896970324</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.04109997541047718</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,31; 6,51</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,68; 6,75</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,27; 0,38</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,75; 3,27</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 2,45</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-0,03; 4,03</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>0.1433258166676082</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.1442517129675439</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.07990891286478864</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.03413413680190047</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.08880752970165928</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.06929352857228359</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-3,34%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>3.073183882256836</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.801570501964135</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-3.045286512552847</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.1611387214649374</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.1736259090818537</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2.071115459576922</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,34; 7,53</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 7,75</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,79; 0,4</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,93; 3,68</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-2,66; 2,76</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-0,03; 4,58</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.3087529648610348</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.6791576361556617</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.273112445515366</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.745752143573807</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-2.423616124676105</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.02895495859483115</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,09</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,84</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2,2</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,54</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.507468238653994</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.747532990751465</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.3844419184591494</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.268235552951926</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>2.450926263528384</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>4.031958411002671</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 11,72</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,4; 10,25</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-3,34; 8,39</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-7,23; 4,86</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-0,79; 7,91</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-2,75; 5,85</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.03462509580496147</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.04283171716466231</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.0334460126853094</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.001769767048189133</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.001932932235991766</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.0230571915069992</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,05%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-0.003385443895614224</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.00754376473543686</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.06791574977640379</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.02934487509050736</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.02663212310885497</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.0002941671235974231</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-1,28; 14,8</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-2,8; 12,99</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-3,73; 9,88</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-8,01; 5,74</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-0,9; 9,57</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-3,15; 7,03</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.07527736737068548</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.07754205018356766</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.004007358933604698</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.0368078605775216</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.02755616289212487</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.04582237278668186</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +920,317 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>3,72</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,8</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,72</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>5.09204131487524</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.842868549754008</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>2.198482840222926</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.9155905887982763</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>3.540558182599585</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.379866615788128</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0,95; 6,29</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>1,33; 6,58</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-3,85; 1,47</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-2,99; 2,18</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-0,57; 3,23</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-0,18; 3,42</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.094559781374108</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.397571917477781</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-3.338368697377324</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-7.232322142959034</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-0.7858607891940212</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-2.751788472960649</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>4,34%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-1,36%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-0,54%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>11.7236328461323</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>10.24809131413275</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>8.394956418120062</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.861871601534632</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>7.914180310352441</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>5.852279729301827</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>1,05; 7,3</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1,48; 7,67</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-4,22; 1,66</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-3,26; 2,46</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-0,64; 3,67</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-0,2; 3,88</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.0614396238264279</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.04636733748046615</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.02522465772558664</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.01050518057119017</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.04159925544885997</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.01621253510749494</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-0.01277624277260561</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.02800370035464462</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.0373248684523143</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.08009193245083751</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.008967768454799574</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.03149415537223429</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.1479633330250737</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.1298697902398588</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.09877902182802188</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.05737117677120075</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.09566080512858514</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.07031649351251687</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>3.723218510400905</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.798694984778117</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-1.231783895752858</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.4842028286305866</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.317114801672514</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1.720290146697689</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.9481250191449773</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.329207670236041</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-3.846997034459728</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-2.988812024621303</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.5723589663844262</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.1820553904854552</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>6.288224609544929</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>6.583713314518833</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.47026432659009</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.175823283416507</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>3.233582104969376</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>3.422051024086823</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.04253926483485659</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.04340161382763374</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.01363896959517261</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.005361352490773396</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.01481956829317298</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.01935591133034564</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>0.0105164209250346</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.01484160803556209</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.04223961740329507</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.03260841855738793</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.00638172458756374</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.002006931451163714</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>0.07301079063658293</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.0767117726082772</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.01662267874975929</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.02462890156883092</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.03667373376679358</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.03884243753760569</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1238,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
